--- a/AKRAM 2026 RUGBY PLAYERS (V2)DATABASE (Responses) (3).xlsx
+++ b/AKRAM 2026 RUGBY PLAYERS (V2)DATABASE (Responses) (3).xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="1067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="1068">
   <si>
     <t>TIMESTAMP</t>
   </si>
@@ -2350,7 +2350,7 @@
     <t>7/15/2026 16:05:04</t>
   </si>
   <si>
-    <t>MUHAMAD SHAHNUR ASYRAF BIN MOHD SHAHFAROL AZUAN</t>
+    <t>MUHAMMAD SHAHNUR ASYRAF BIN MOHD SHAHFAROL AZUAN</t>
   </si>
   <si>
     <t>130211-04-0033</t>
@@ -3263,6 +3263,9 @@
   </si>
   <si>
     <t>BILANGAN</t>
+  </si>
+  <si>
+    <t>MUHAMAD SHAHNUR ASYRAF BIN MOHD SHAHFAROL AZUAN</t>
   </si>
   <si>
     <t>(blank)</t>
@@ -4133,7 +4136,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4147,7 +4150,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4161,7 +4164,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4175,7 +4178,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4189,7 +4192,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4203,7 +4206,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4217,7 +4220,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4231,7 +4234,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4245,7 +4248,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4259,7 +4262,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4273,7 +4276,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4287,7 +4290,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4301,7 +4304,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4315,7 +4318,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4329,7 +4332,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4343,7 +4346,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4357,7 +4360,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4371,7 +4374,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4385,7 +4388,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4399,7 +4402,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4413,7 +4416,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4427,7 +4430,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4441,7 +4444,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4455,7 +4458,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4469,7 +4472,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4483,7 +4486,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4497,7 +4500,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4511,7 +4514,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4525,7 +4528,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4539,7 +4542,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4553,7 +4556,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4567,7 +4570,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -4620,7 +4623,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{2DE19A8E-DC74-40B1-6346-716A7A75BDA4}">
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{E5CA0459-E5FC-DEE0-B448-716AC80B8715}">
       <tableStyleElement type="wholeTable" dxfId="35"/>
       <tableStyleElement type="headerRow" dxfId="34"/>
       <tableStyleElement type="firstRowStripe" dxfId="33"/>
@@ -4636,13 +4639,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" invalid="1" refreshOnLoad="1" refreshedVersion="5" refreshedDate="46238.4129976852" refreshedBy="izzulwaqiuddinazhadbintammizi" recordCount="58">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" invalid="1" refreshOnLoad="1" refreshedVersion="5" refreshedDate="46238.4198611111" refreshedBy="izzulwaqiuddinazhadbintammizi" recordCount="61">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:AF159" sheet="Form Responses 1"/>
   </cacheSource>
   <cacheFields count="32">
     <cacheField name="TIMESTAMP" numFmtId="49">
-      <sharedItems containsBlank="1" count="58">
+      <sharedItems containsBlank="1" count="61">
         <s v="7/15/2026 12:30:56"/>
         <s v="7/16/2026 8:57:33"/>
         <s v="7/17/2026 13:11:14"/>
@@ -4700,11 +4703,14 @@
         <s v="7/21/2026 6:15:46"/>
         <s v="7/24/2026 10:30:49"/>
         <s v="7/28/2026 10:18:49"/>
+        <s v="8/2/2026 15:46:18"/>
+        <s v="8/2/2026 18:09:07"/>
+        <s v="8/3/2026 15:48:55"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NAMA PENUH" numFmtId="49">
-      <sharedItems containsBlank="1" count="58">
+      <sharedItems containsBlank="1" count="61">
         <s v="AIMAN ZAINI BIN ZAINAL"/>
         <s v="AHMAD ZAHID BIN NANI DZULKARNAIN"/>
         <s v="NAJMI BIN ROSLAN"/>
@@ -4762,11 +4768,14 @@
         <s v="MUHAMMAD KHALIFF BIN MOHD KHAIRI"/>
         <s v="MUHAMMAD SYAQIB BIN AZIZUL"/>
         <s v="MUHAMMAD HAMZAH BIN ABDUL MALEK"/>
+        <s v="ARIEL IRFAN BIN HAMRIE "/>
+        <s v="MUHAMMAD RAYYAN MIKAIL BIN MOHD RAZMI "/>
+        <s v="MUHAMMAD AMZAR BIN MOHD ZAMRI"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NOMBOR KAD PENGENALAN" numFmtId="49">
-      <sharedItems containsBlank="1" count="58">
+      <sharedItems containsBlank="1" count="61">
         <s v="100223-04-0367"/>
         <s v="100106-04-0245"/>
         <s v="100213-04-0291"/>
@@ -4824,11 +4833,14 @@
         <s v="110228-04-0373"/>
         <s v="110601-04-0217"/>
         <s v="130103-04-0431"/>
+        <s v="110112020119"/>
+        <s v="130406-04-0287"/>
+        <s v="130812031397"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NAMA SAMARAN" numFmtId="49">
-      <sharedItems containsBlank="1" count="55">
+      <sharedItems containsBlank="1" count="58">
         <s v="AIMAN"/>
         <s v="ZAHID"/>
         <s v="MII"/>
@@ -4883,11 +4895,14 @@
         <s v="KHEE"/>
         <s v="TOYOL"/>
         <s v="HAMZAH"/>
+        <s v="AREL"/>
+        <s v="PANJANG"/>
+        <s v="AMZAR"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="TARIKH LAHIR" numFmtId="49">
-      <sharedItems containsBlank="1" count="57">
+      <sharedItems containsBlank="1" count="59">
         <s v="2/23/2010"/>
         <s v="1/6/2010"/>
         <s v="2/13/2010"/>
@@ -4944,6 +4959,8 @@
         <s v="2/28/2011"/>
         <s v="6/1/2011"/>
         <s v="3/1/2013"/>
+        <s v="4/6/2013"/>
+        <s v="8/13/2012"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -4969,7 +4986,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="NOMBOR TELEFON PEMAIN" numFmtId="49">
-      <sharedItems containsBlank="1" count="58">
+      <sharedItems containsBlank="1" count="61">
         <s v="019-257 2956"/>
         <s v="011-2050 3344"/>
         <s v="011-1502 9313"/>
@@ -5027,11 +5044,14 @@
         <s v="011-1289 8310"/>
         <s v="109265992"/>
         <s v="013-763 1050"/>
+        <s v="01126663671"/>
+        <s v="017-8409231"/>
+        <s v="132696211"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="ALAMAT RUMAH" numFmtId="49">
-      <sharedItems containsBlank="1" count="58">
+      <sharedItems containsBlank="1" count="61">
         <s v="KM 16, KAMPUNG PULAI, 77300 MERLIMAU, MELAKA"/>
         <s v="NO. 36 JALAN TBC 24A, TAMAN BUKIT CHENG, 75250 CHENG, MELAKA"/>
         <s v="NO 10 , JALAN PRP6, TAMAN PAYA RUMPUT PERMAI,76450 MELAKA TENGAH, MELAKA"/>
@@ -5089,11 +5109,14 @@
         <s v="NO 2, JLN BP 3C, TAMAN BERTAM PERDANA, 75260 MELAKA"/>
         <s v="NO 11, JALAN KS 1/4, TAMAN KERJASAMA SEKSYEN 1, BUKIT BERUANG 75450 MELAKA"/>
         <s v="NO 48- 1, BATU 3 1/ 4, SOLOK PASIR PUTEH, LORONG HJ BABA, BACHANG DARAT, 75350 MELAKA."/>
+        <s v="NO 5B, BLOCK I RUMAH AWAM AYER MOLEK, 75460 MELAKA"/>
+        <s v="877-1,BATU 9 TANGGA BATU 76400 TG.KLING MELAKA"/>
+        <s v="LOT 472 JLN DEMANG MOHAMMAD, PAYA RUMPUT 76450 MELAKA"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NAMA PENUH  IBU BAPA / PENJAGA 1" numFmtId="49">
-      <sharedItems containsBlank="1" count="57">
+      <sharedItems containsBlank="1" count="60">
         <s v="ZAINAL BIN ISHAK"/>
         <s v="NANI DZULKARNAIN BIN MOHD YUNAN"/>
         <s v="AZURA BINTI MOHD BIZAN"/>
@@ -5150,11 +5173,14 @@
         <s v="NURSYAFIKA BTE TUSOF"/>
         <s v="AZIZUL BIN ABD AZIZ"/>
         <s v="NORA BINTI ISMAIL"/>
+        <s v="HAMRIE BIN ABU MANSOR"/>
+        <s v="MOHD RAZMI BIN ZAINAL "/>
+        <s v="MOHD ZAMRI BIN YAACOB"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NOMBOR KAD PENGENALAN  IBU BAPA / PENJAGA 1" numFmtId="49">
-      <sharedItems containsBlank="1" count="57">
+      <sharedItems containsBlank="1" count="60">
         <s v="710223-04-5289"/>
         <s v="740531-05-5267"/>
         <s v="771209-01-5728"/>
@@ -5211,11 +5237,14 @@
         <s v="881213-04-5222"/>
         <s v="790706-04-5243"/>
         <s v="730215-01-5677"/>
+        <s v="810626045617"/>
+        <s v="780809-04-5351"/>
+        <s v="860210295127"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NO TELEFON IBU BAPA / PENJAGA 1" numFmtId="49">
-      <sharedItems containsBlank="1" count="57">
+      <sharedItems containsBlank="1" count="60">
         <s v="0172522771"/>
         <s v="0126627714"/>
         <s v="0196290706"/>
@@ -5272,11 +5301,14 @@
         <s v="0173258835"/>
         <s v="0126571277"/>
         <s v="0108054467"/>
+        <s v="01162069722"/>
+        <s v="012-3576228"/>
+        <s v="0139946211"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="PEKERJAAN / ALAMAT TEMPAT KERJA /NO TELEFON PEJABAT IBU BAPA / PENJAGA 1" numFmtId="49">
-      <sharedItems containsBlank="1" count="52">
+      <sharedItems containsBlank="1" count="55">
         <s v="PEKERJA AM SWASTA/SK MERLIMAU/0127716712"/>
         <s v="PEGAWAI PERTANIAN / WISMA TANI PUTRAJAYA / 0388703448"/>
         <s v="SURI RUMAH"/>
@@ -5328,11 +5360,14 @@
         <s v="NURSE, SINGAPORE"/>
         <s v="PENYELIA KESELAMATAN / PETRONAS TWIN TOWER (KLCC), KUALA LUMPUR"/>
         <s v="ORNAPAPER, BATU BERENDAM, 73530 MELAKA"/>
+        <s v="Bekerja sendiri"/>
+        <s v="PEGAWAI PENDAFTARAN/JAB.PENDAFTARAN NEGARA,ARAS 1,KOMPLEKS KDN,JALAN SERI NEGERI,75450,AYER KEROH,MELAKA"/>
+        <s v="Petronas Melaka Sg Udang"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NAMA PENUH  IBU BAPA / PENJAGA 2" numFmtId="49">
-      <sharedItems containsBlank="1" count="56">
+      <sharedItems containsBlank="1" count="59">
         <s v="ROSNANI BINTI PIT"/>
         <s v="AZIZAH BINTI AHMAD"/>
         <s v="ROSLAN BIN SULAIMAN"/>
@@ -5388,11 +5423,14 @@
         <s v="YUSOF BIN AB HAMIT"/>
         <s v="NORFAZILAH BINTI ABU SAMAH"/>
         <s v="-"/>
+        <s v="NOR ROSFAZILAH BINTI ISHAK"/>
+        <s v="Mastura Binti Abd Rahim "/>
+        <s v="SITI NURAIN BINTI MUSTAFA"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NOMBOR KAD PENGENALAN  IBU BAPA / PENJAGA 2" numFmtId="49">
-      <sharedItems containsBlank="1" count="56">
+      <sharedItems containsBlank="1" count="59">
         <s v="740323-04-5072"/>
         <s v="760124-04-5094"/>
         <s v="730731-01-6669"/>
@@ -5448,11 +5486,14 @@
         <s v="570831-04-5467"/>
         <s v="830108-04-5124"/>
         <s v="-"/>
+        <s v="831218025444"/>
+        <s v="760903-04-5288"/>
+        <s v="900814035012"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="NO TELEFON IBU BAPA / PENJAGA 2" numFmtId="49">
-      <sharedItems containsBlank="1" count="56">
+      <sharedItems containsBlank="1" count="59">
         <s v="0196602480"/>
         <s v="0136313324"/>
         <s v="0183610542"/>
@@ -5508,11 +5549,14 @@
         <s v="143381957"/>
         <s v="122082401"/>
         <s v="-"/>
+        <s v="0182604544"/>
+        <s v="019-6257200"/>
+        <s v="0136527991"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="PEKERJAAN / ALAMAT TEMPAT KERJA /NO TELEFON PEJABAT IBU BAPA / PENJAGA 2 (JIKA ADA)" numFmtId="49">
-      <sharedItems containsBlank="1" count="41">
+      <sharedItems containsBlank="1" count="43">
         <s v="SURI RUMAH TANGGA"/>
         <s v="GURU / SMK KLEBANG BESAR / 063151014"/>
         <s v="PESARA ASKAR"/>
@@ -5554,10 +5598,12 @@
         <s v="PESARA, LOT 345-1 KAMPUNG PERMATANG, KLEBANG BESAR 75200 MELAKA"/>
         <s v="PENOLONG PEGAWAI PEMBANGUNAN MASYARAKAT / JABATAN KEBAJIKAN MASYARAKAT NEGERI MELAKA / 06-3333333"/>
         <s v="-"/>
+        <s v="Bekerja sendiri"/>
+        <s v="Leader/Recron Malaysia Sdn Bhd,kaw perindustrian Tangga Batu,76400 Tg.Kling ,Melaka"/>
       </sharedItems>
     </cacheField>
     <cacheField name="EMERGENCY CONTACT DETAIL SELAIN YANG DI ATAS (SAUDARA MARA, JIRAN, MAJIKAN) SERTAKAN NAMA, HUBUNGAN DAN NO TELEFON YANG BOLEH DIHUBUNGI. ISIKAN BEBERAPA NAMA JIKA ADA_x000a__x000a_(CONTOH: PAK ALI, DATUK, 0123456687)" numFmtId="49">
-      <sharedItems containsBlank="1" count="57">
+      <sharedItems containsBlank="1" count="60">
         <s v="ABDUL AZIZ BIN ISHAK/BAPA SAUDARA/0196592825_x000a_ROSNITAH BINTI PIT/IBU SAUDARA/0196385289"/>
         <s v="ENCIK AZHARI AHMAD (PAKCIK) 0149628203; PUAN NURDIANA AZHARI (SEPUPU) 0183885736"/>
         <s v="IBU, 0196290706"/>
@@ -5615,6 +5661,9 @@
         <s v="DATUK, 0143381957"/>
         <s v="ABU SAMAH - DATUK 0107935293"/>
         <s v="KHAIRI, ABANG, 01162662410"/>
+        <s v="01131762917"/>
+        <s v="Muhammad Azri-bapa saudara-013-6359554_x000a_Fariza-Ibu saudara-017-2118717_x000a_"/>
+        <s v="01137367740 (bapa saudara) "/>
       </sharedItems>
     </cacheField>
     <cacheField name="KUMPULAN DARAH " numFmtId="49">
@@ -5661,7 +5710,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="SEKIRANYA ADA, TERANGKAN SEJARAH PENYAKIT TERSEBUT " numFmtId="49">
-      <sharedItems containsBlank="1" count="10">
+      <sharedItems containsBlank="1" count="11">
         <m/>
         <s v="DIBAWA HOSPITAL MELAKA UNTUK PEMERHATIAN - CONCUSSION DALAM PERLAWANAN SSR2025 DI POLITEKNIK MERLIMAU. KELUAR HOSPITAL SELEPAS 5-6 JAM PEMERHATIAN DI WAD"/>
         <s v="TIADA"/>
@@ -5672,10 +5721,11 @@
         <s v="MASALAH LUTUT - TELAH DIRUJUK KE HOSPITAL PUTRA MELAKA (BERLAKU KETIKA BERMAIN RAGBI SEJAK DARJAH 6). DR NASIHATKAN UNTUK BEREHAT SELAMA 2 BULAN TANPA SEBARANG TRAINING &amp; PERLAWANAN. ALHAMDULILLAH TELAH KEMBALI PULIH NAMUN MASIH PERLU DIPANTAU DARI MASA K"/>
         <s v="MDI SULBUTAMOL BILA PERLU"/>
         <s v="CHILDHOOD ASTHMA"/>
+        <s v="Retak tahun 2020/2021 umur 7 tahun"/>
       </sharedItems>
     </cacheField>
     <cacheField name="TINGGI (CM)" numFmtId="49">
-      <sharedItems containsBlank="1" count="28">
+      <sharedItems containsBlank="1" count="30">
         <s v="165"/>
         <s v="163"/>
         <s v="168"/>
@@ -5704,10 +5754,12 @@
         <s v="155"/>
         <m/>
         <s v="154"/>
+        <s v="172 cm"/>
+        <s v="168cm"/>
       </sharedItems>
     </cacheField>
     <cacheField name="BERAT (KG)" numFmtId="49">
-      <sharedItems containsBlank="1" count="37">
+      <sharedItems containsBlank="1" count="39">
         <s v="55"/>
         <s v="63"/>
         <s v="56"/>
@@ -5745,6 +5797,8 @@
         <s v="54"/>
         <s v="37"/>
         <m/>
+        <s v="58"/>
+        <s v="56kg"/>
       </sharedItems>
     </cacheField>
     <cacheField name="UBAT-UBATAN YANG MASIH DIAMBIL" numFmtId="49">
@@ -5821,7 +5875,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="58">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="61">
   <r>
     <x v="0"/>
     <x v="0"/>
@@ -7765,9 +7819,9 @@
     <x v="57"/>
     <x v="57"/>
     <x v="54"/>
-    <x v="56"/>
-    <x v="4"/>
-    <x v="7"/>
+    <x v="13"/>
+    <x v="1"/>
+    <x v="0"/>
     <x v="57"/>
     <x v="57"/>
     <x v="56"/>
@@ -7777,6 +7831,108 @@
     <x v="55"/>
     <x v="55"/>
     <x v="55"/>
+    <x v="41"/>
+    <x v="57"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="37"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="9"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <x v="58"/>
+    <x v="58"/>
+    <x v="55"/>
+    <x v="56"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="58"/>
+    <x v="58"/>
+    <x v="57"/>
+    <x v="57"/>
+    <x v="57"/>
+    <x v="52"/>
+    <x v="56"/>
+    <x v="56"/>
+    <x v="56"/>
+    <x v="42"/>
+    <x v="58"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="10"/>
+    <x v="28"/>
+    <x v="38"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="9"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <x v="59"/>
+    <x v="59"/>
+    <x v="56"/>
+    <x v="57"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="59"/>
+    <x v="59"/>
+    <x v="58"/>
+    <x v="58"/>
+    <x v="58"/>
+    <x v="53"/>
+    <x v="57"/>
+    <x v="57"/>
+    <x v="57"/>
+    <x v="6"/>
+    <x v="59"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="29"/>
+    <x v="32"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="9"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <x v="60"/>
+    <x v="60"/>
+    <x v="57"/>
+    <x v="58"/>
+    <x v="4"/>
+    <x v="7"/>
+    <x v="60"/>
+    <x v="60"/>
+    <x v="59"/>
+    <x v="59"/>
+    <x v="59"/>
+    <x v="54"/>
+    <x v="58"/>
+    <x v="58"/>
+    <x v="58"/>
     <x v="4"/>
     <x v="23"/>
     <x v="0"/>
@@ -7799,11 +7955,76 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Sheet1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="" updatedVersion="5" compact="0" compactData="0" showDrill="1">
-  <location ref="A1:C60" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+  <location ref="A1:C63" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="32">
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" numFmtId="49" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" numFmtId="49" showAll="0">
+      <items count="62">
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="15"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="38"/>
+        <item x="17"/>
+        <item x="39"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="18"/>
+        <item x="0"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="40"/>
+        <item x="23"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="45"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="30"/>
+        <item x="46"/>
+        <item x="10"/>
+        <item x="47"/>
+        <item x="11"/>
+        <item x="48"/>
+        <item x="12"/>
+        <item x="49"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="33"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="14"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="34"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="60"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" numFmtId="49" showAll="0">
-      <items count="59">
+      <items count="62">
         <item x="27"/>
         <item x="18"/>
         <item x="22"/>
@@ -7861,7 +8082,10 @@
         <item x="43"/>
         <item x="26"/>
         <item x="41"/>
+        <item x="60"/>
         <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -7908,7 +8132,7 @@
     <field x="5"/>
     <field x="1"/>
   </rowFields>
-  <rowItems count="59">
+  <rowItems count="62">
     <i>
       <x/>
       <x v="7"/>
@@ -7969,6 +8193,9 @@
     </i>
     <i r="1">
       <x v="56"/>
+    </i>
+    <i r="1">
+      <x v="59"/>
     </i>
     <i>
       <x v="1"/>
@@ -8031,6 +8258,9 @@
     <i r="1">
       <x v="55"/>
     </i>
+    <i r="1">
+      <x v="60"/>
+    </i>
     <i>
       <x v="2"/>
       <x v="3"/>
@@ -8073,6 +8303,9 @@
     </i>
     <i r="1">
       <x v="53"/>
+    </i>
+    <i r="1">
+      <x v="58"/>
     </i>
     <i>
       <x v="3"/>
@@ -16977,7 +17210,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultColWidth="12.6339285714286" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -17018,7 +17251,7 @@
     <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>764</v>
+        <v>1065</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
@@ -17178,29 +17411,29 @@
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="C22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="C23" s="5">
+      <c r="C23" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:3">
       <c r="A24" s="3"/>
       <c r="B24" s="4" t="s">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="C24" s="5">
         <v>1</v>
@@ -17209,7 +17442,7 @@
     <row r="25" customHeight="1" spans="1:3">
       <c r="A25" s="3"/>
       <c r="B25" s="4" t="s">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="C25" s="5">
         <v>1</v>
@@ -17218,7 +17451,7 @@
     <row r="26" customHeight="1" spans="1:3">
       <c r="A26" s="3"/>
       <c r="B26" s="4" t="s">
-        <v>594</v>
+        <v>404</v>
       </c>
       <c r="C26" s="5">
         <v>1</v>
@@ -17227,7 +17460,7 @@
     <row r="27" customHeight="1" spans="1:3">
       <c r="A27" s="3"/>
       <c r="B27" s="4" t="s">
-        <v>386</v>
+        <v>594</v>
       </c>
       <c r="C27" s="5">
         <v>1</v>
@@ -17236,7 +17469,7 @@
     <row r="28" customHeight="1" spans="1:3">
       <c r="A28" s="3"/>
       <c r="B28" s="4" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="C28" s="5">
         <v>1</v>
@@ -17245,7 +17478,7 @@
     <row r="29" customHeight="1" spans="1:3">
       <c r="A29" s="3"/>
       <c r="B29" s="4" t="s">
-        <v>610</v>
+        <v>357</v>
       </c>
       <c r="C29" s="5">
         <v>1</v>
@@ -17254,7 +17487,7 @@
     <row r="30" customHeight="1" spans="1:3">
       <c r="A30" s="3"/>
       <c r="B30" s="4" t="s">
-        <v>483</v>
+        <v>610</v>
       </c>
       <c r="C30" s="5">
         <v>1</v>
@@ -17263,7 +17496,7 @@
     <row r="31" customHeight="1" spans="1:3">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>420</v>
+        <v>483</v>
       </c>
       <c r="C31" s="5">
         <v>1</v>
@@ -17272,7 +17505,7 @@
     <row r="32" customHeight="1" spans="1:3">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>536</v>
+        <v>420</v>
       </c>
       <c r="C32" s="5">
         <v>1</v>
@@ -17281,7 +17514,7 @@
     <row r="33" customHeight="1" spans="1:3">
       <c r="A33" s="3"/>
       <c r="B33" s="4" t="s">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="C33" s="5">
         <v>1</v>
@@ -17290,7 +17523,7 @@
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="3"/>
       <c r="B34" s="4" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="C34" s="5">
         <v>1</v>
@@ -17299,7 +17532,7 @@
     <row r="35" customHeight="1" spans="1:3">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>628</v>
+        <v>579</v>
       </c>
       <c r="C35" s="5">
         <v>1</v>
@@ -17308,7 +17541,7 @@
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
-        <v>466</v>
+        <v>628</v>
       </c>
       <c r="C36" s="5">
         <v>1</v>
@@ -17317,7 +17550,7 @@
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="3"/>
       <c r="B37" s="4" t="s">
-        <v>552</v>
+        <v>466</v>
       </c>
       <c r="C37" s="5">
         <v>1</v>
@@ -17326,7 +17559,7 @@
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="3"/>
       <c r="B38" s="4" t="s">
-        <v>322</v>
+        <v>552</v>
       </c>
       <c r="C38" s="5">
         <v>1</v>
@@ -17335,7 +17568,7 @@
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="3"/>
       <c r="B39" s="4" t="s">
-        <v>454</v>
+        <v>322</v>
       </c>
       <c r="C39" s="5">
         <v>1</v>
@@ -17344,7 +17577,7 @@
     <row r="40" customHeight="1" spans="1:3">
       <c r="A40" s="3"/>
       <c r="B40" s="4" t="s">
-        <v>340</v>
+        <v>454</v>
       </c>
       <c r="C40" s="5">
         <v>1</v>
@@ -17353,45 +17586,45 @@
     <row r="41" customHeight="1" spans="1:3">
       <c r="A41" s="3"/>
       <c r="B41" s="4" t="s">
-        <v>501</v>
+        <v>340</v>
       </c>
       <c r="C41" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:3">
-      <c r="A42" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" s="2">
+      <c r="A42" s="3"/>
+      <c r="B42" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C42" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:3">
       <c r="A43" s="3"/>
       <c r="B43" s="4" t="s">
-        <v>252</v>
+        <v>1049</v>
       </c>
       <c r="C43" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:3">
-      <c r="A44" s="3"/>
-      <c r="B44" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C44" s="5">
+      <c r="A44" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:3">
       <c r="A45" s="3"/>
       <c r="B45" s="4" t="s">
-        <v>123</v>
+        <v>252</v>
       </c>
       <c r="C45" s="5">
         <v>1</v>
@@ -17400,7 +17633,7 @@
     <row r="46" customHeight="1" spans="1:3">
       <c r="A46" s="3"/>
       <c r="B46" s="4" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="C46" s="5">
         <v>1</v>
@@ -17409,7 +17642,7 @@
     <row r="47" customHeight="1" spans="1:3">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>305</v>
+        <v>123</v>
       </c>
       <c r="C47" s="5">
         <v>1</v>
@@ -17418,7 +17651,7 @@
     <row r="48" customHeight="1" spans="1:3">
       <c r="A48" s="3"/>
       <c r="B48" s="4" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C48" s="5">
         <v>1</v>
@@ -17427,7 +17660,7 @@
     <row r="49" customHeight="1" spans="1:3">
       <c r="A49" s="3"/>
       <c r="B49" s="4" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="C49" s="5">
         <v>1</v>
@@ -17436,7 +17669,7 @@
     <row r="50" customHeight="1" spans="1:3">
       <c r="A50" s="3"/>
       <c r="B50" s="4" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="C50" s="5">
         <v>1</v>
@@ -17445,7 +17678,7 @@
     <row r="51" customHeight="1" spans="1:3">
       <c r="A51" s="3"/>
       <c r="B51" s="4" t="s">
-        <v>966</v>
+        <v>272</v>
       </c>
       <c r="C51" s="5">
         <v>1</v>
@@ -17454,7 +17687,7 @@
     <row r="52" customHeight="1" spans="1:3">
       <c r="A52" s="3"/>
       <c r="B52" s="4" t="s">
-        <v>985</v>
+        <v>159</v>
       </c>
       <c r="C52" s="5">
         <v>1</v>
@@ -17463,7 +17696,7 @@
     <row r="53" customHeight="1" spans="1:3">
       <c r="A53" s="3"/>
       <c r="B53" s="4" t="s">
-        <v>176</v>
+        <v>966</v>
       </c>
       <c r="C53" s="5">
         <v>1</v>
@@ -17472,7 +17705,7 @@
     <row r="54" customHeight="1" spans="1:3">
       <c r="A54" s="3"/>
       <c r="B54" s="4" t="s">
-        <v>101</v>
+        <v>985</v>
       </c>
       <c r="C54" s="5">
         <v>1</v>
@@ -17481,27 +17714,25 @@
     <row r="55" customHeight="1" spans="1:3">
       <c r="A55" s="3"/>
       <c r="B55" s="4" t="s">
-        <v>288</v>
+        <v>176</v>
       </c>
       <c r="C55" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:3">
-      <c r="A56" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C56" s="2">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:3">
       <c r="A57" s="3"/>
       <c r="B57" s="4" t="s">
-        <v>33</v>
+        <v>288</v>
       </c>
       <c r="C57" s="5">
         <v>1</v>
@@ -17510,7 +17741,7 @@
     <row r="58" customHeight="1" spans="1:3">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>83</v>
+        <v>1014</v>
       </c>
       <c r="C58" s="5">
         <v>1</v>
@@ -17518,20 +17749,49 @@
     </row>
     <row r="59" customHeight="1" spans="1:3">
       <c r="A59" s="1" t="s">
-        <v>1065</v>
+        <v>37</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" customHeight="1" spans="1:3">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="3"/>
+      <c r="B60" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:3">
+      <c r="A61" s="3"/>
+      <c r="B61" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:3">
+      <c r="A62" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="8">
-        <v>57</v>
+      <c r="B62" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:3">
+      <c r="A63" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B63" s="7"/>
+      <c r="C63" s="8">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/AKRAM 2026 RUGBY PLAYERS (V2)DATABASE (Responses) (3).xlsx
+++ b/AKRAM 2026 RUGBY PLAYERS (V2)DATABASE (Responses) (3).xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="1067">
   <si>
     <t>TIMESTAMP</t>
   </si>
@@ -3263,9 +3263,6 @@
   </si>
   <si>
     <t>BILANGAN</t>
-  </si>
-  <si>
-    <t>MUHAMAD SHAHNUR ASYRAF BIN MOHD SHAHFAROL AZUAN</t>
   </si>
   <si>
     <t>(blank)</t>
@@ -4623,7 +4620,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{E5CA0459-E5FC-DEE0-B448-716AC80B8715}">
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{961432D2-082F-01B7-D94A-716A76B5B4F5}">
       <tableStyleElement type="wholeTable" dxfId="35"/>
       <tableStyleElement type="headerRow" dxfId="34"/>
       <tableStyleElement type="firstRowStripe" dxfId="33"/>
@@ -4639,7 +4636,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" invalid="1" refreshOnLoad="1" refreshedVersion="5" refreshedDate="46238.4198611111" refreshedBy="izzulwaqiuddinazhadbintammizi" recordCount="61">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" invalid="1" refreshOnLoad="1" refreshedVersion="5" refreshedDate="46238.4262152778" refreshedBy="izzulwaqiuddinazhadbintammizi" recordCount="61">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:AF159" sheet="Form Responses 1"/>
   </cacheSource>
@@ -4710,7 +4707,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="NAMA PENUH" numFmtId="49">
-      <sharedItems containsBlank="1" count="61">
+      <sharedItems containsBlank="1" count="62">
         <s v="AIMAN ZAINI BIN ZAINAL"/>
         <s v="AHMAD ZAHID BIN NANI DZULKARNAIN"/>
         <s v="NAJMI BIN ROSLAN"/>
@@ -4753,7 +4750,7 @@
         <s v="MUHAMMAD KHAIRUL ZAQWAN BIN KHAIRUL NIZAM"/>
         <s v="MUHAMMAD ADAM BIN MOHD RAIME"/>
         <s v="WAN MUHAMMAD FARIS BIN WAN MOHD KHAIRI"/>
-        <s v="MUHAMAD SHAHNUR ASYRAF BIN MOHD SHAHFAROL AZUAN"/>
+        <s v="MUHAMMAD SHAHNUR ASYRAF BIN MOHD SHAHFAROL AZUAN"/>
         <s v="SYED MUNEEB HASAN SHAH BIN SYED ANWAR SHAH"/>
         <s v="MUHAMMAD MAHDI BIN ZULKHARI"/>
         <s v="MUHAMMAD FIRAS HAMIZAN BIN AZUAN"/>
@@ -4772,6 +4769,7 @@
         <s v="MUHAMMAD RAYYAN MIKAIL BIN MOHD RAZMI "/>
         <s v="MUHAMMAD AMZAR BIN MOHD ZAMRI"/>
         <m/>
+        <s v="MUHAMAD SHAHNUR ASYRAF BIN MOHD SHAHFAROL AZUAN" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="NOMBOR KAD PENGENALAN" numFmtId="49">
@@ -8024,7 +8022,7 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" numFmtId="49" showAll="0">
-      <items count="62">
+      <items count="63">
         <item x="27"/>
         <item x="18"/>
         <item x="22"/>
@@ -8036,7 +8034,7 @@
         <item x="11"/>
         <item x="35"/>
         <item x="32"/>
-        <item x="42"/>
+        <item m="1" x="61"/>
         <item x="40"/>
         <item x="19"/>
         <item x="17"/>
@@ -8086,6 +8084,7 @@
         <item x="57"/>
         <item x="58"/>
         <item x="59"/>
+        <item x="42"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -8141,9 +8140,6 @@
       <x v="9"/>
     </i>
     <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
       <x v="12"/>
     </i>
     <i r="1">
@@ -8196,6 +8192,9 @@
     </i>
     <i r="1">
       <x v="59"/>
+    </i>
+    <i r="1">
+      <x v="61"/>
     </i>
     <i>
       <x v="1"/>
@@ -13679,9 +13678,15 @@
         <v>51</v>
       </c>
       <c r="Z59" s="20"/>
-      <c r="AA59" s="20"/>
-      <c r="AB59" s="20"/>
-      <c r="AC59" s="20"/>
+      <c r="AA59" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB59" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC59" s="20" t="s">
+        <v>120</v>
+      </c>
       <c r="AD59" s="20"/>
       <c r="AE59" s="20"/>
       <c r="AF59" s="20"/>
@@ -13765,8 +13770,12 @@
       <c r="Z60" s="20" t="s">
         <v>1027</v>
       </c>
-      <c r="AA60" s="20"/>
-      <c r="AB60" s="20"/>
+      <c r="AA60" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB60" s="20" t="s">
+        <v>99</v>
+      </c>
       <c r="AC60" s="20"/>
       <c r="AD60" s="20"/>
       <c r="AE60" s="20"/>
@@ -13849,9 +13858,15 @@
       <c r="Z61" s="20" t="s">
         <v>1027</v>
       </c>
-      <c r="AA61" s="20"/>
-      <c r="AB61" s="20"/>
-      <c r="AC61" s="20"/>
+      <c r="AA61" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB61" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC61" s="20" t="s">
+        <v>81</v>
+      </c>
       <c r="AD61" s="20"/>
       <c r="AE61" s="20"/>
       <c r="AF61" s="20"/>
@@ -17251,7 +17266,7 @@
     <row r="4" customHeight="1" spans="1:3">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>1065</v>
+        <v>728</v>
       </c>
       <c r="C4" s="5">
         <v>1</v>
@@ -17260,7 +17275,7 @@
     <row r="5" customHeight="1" spans="1:3">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>728</v>
+        <v>902</v>
       </c>
       <c r="C5" s="5">
         <v>1</v>
@@ -17269,7 +17284,7 @@
     <row r="6" customHeight="1" spans="1:3">
       <c r="A6" s="3"/>
       <c r="B6" s="4" t="s">
-        <v>902</v>
+        <v>934</v>
       </c>
       <c r="C6" s="5">
         <v>1</v>
@@ -17278,7 +17293,7 @@
     <row r="7" customHeight="1" spans="1:3">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>934</v>
+        <v>701</v>
       </c>
       <c r="C7" s="5">
         <v>1</v>
@@ -17287,7 +17302,7 @@
     <row r="8" customHeight="1" spans="1:3">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>701</v>
+        <v>818</v>
       </c>
       <c r="C8" s="5">
         <v>1</v>
@@ -17296,7 +17311,7 @@
     <row r="9" customHeight="1" spans="1:3">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>818</v>
+        <v>1002</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -17305,7 +17320,7 @@
     <row r="10" customHeight="1" spans="1:3">
       <c r="A10" s="3"/>
       <c r="B10" s="4" t="s">
-        <v>1002</v>
+        <v>683</v>
       </c>
       <c r="C10" s="5">
         <v>1</v>
@@ -17314,7 +17329,7 @@
     <row r="11" customHeight="1" spans="1:3">
       <c r="A11" s="3"/>
       <c r="B11" s="4" t="s">
-        <v>683</v>
+        <v>834</v>
       </c>
       <c r="C11" s="5">
         <v>1</v>
@@ -17323,7 +17338,7 @@
     <row r="12" customHeight="1" spans="1:3">
       <c r="A12" s="3"/>
       <c r="B12" s="4" t="s">
-        <v>834</v>
+        <v>713</v>
       </c>
       <c r="C12" s="5">
         <v>1</v>
@@ -17332,7 +17347,7 @@
     <row r="13" customHeight="1" spans="1:3">
       <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>713</v>
+        <v>798</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
@@ -17341,7 +17356,7 @@
     <row r="14" customHeight="1" spans="1:3">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>798</v>
+        <v>666</v>
       </c>
       <c r="C14" s="5">
         <v>1</v>
@@ -17350,7 +17365,7 @@
     <row r="15" customHeight="1" spans="1:3">
       <c r="A15" s="3"/>
       <c r="B15" s="4" t="s">
-        <v>666</v>
+        <v>884</v>
       </c>
       <c r="C15" s="5">
         <v>1</v>
@@ -17359,7 +17374,7 @@
     <row r="16" customHeight="1" spans="1:3">
       <c r="A16" s="3"/>
       <c r="B16" s="4" t="s">
-        <v>884</v>
+        <v>950</v>
       </c>
       <c r="C16" s="5">
         <v>1</v>
@@ -17368,7 +17383,7 @@
     <row r="17" customHeight="1" spans="1:3">
       <c r="A17" s="3"/>
       <c r="B17" s="4" t="s">
-        <v>950</v>
+        <v>919</v>
       </c>
       <c r="C17" s="5">
         <v>1</v>
@@ -17377,7 +17392,7 @@
     <row r="18" customHeight="1" spans="1:3">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>919</v>
+        <v>868</v>
       </c>
       <c r="C18" s="5">
         <v>1</v>
@@ -17386,7 +17401,7 @@
     <row r="19" customHeight="1" spans="1:3">
       <c r="A19" s="3"/>
       <c r="B19" s="4" t="s">
-        <v>868</v>
+        <v>782</v>
       </c>
       <c r="C19" s="5">
         <v>1</v>
@@ -17395,7 +17410,7 @@
     <row r="20" customHeight="1" spans="1:3">
       <c r="A20" s="3"/>
       <c r="B20" s="4" t="s">
-        <v>782</v>
+        <v>746</v>
       </c>
       <c r="C20" s="5">
         <v>1</v>
@@ -17404,7 +17419,7 @@
     <row r="21" customHeight="1" spans="1:3">
       <c r="A21" s="3"/>
       <c r="B21" s="4" t="s">
-        <v>746</v>
+        <v>1030</v>
       </c>
       <c r="C21" s="5">
         <v>1</v>
@@ -17413,7 +17428,7 @@
     <row r="22" customHeight="1" spans="1:3">
       <c r="A22" s="3"/>
       <c r="B22" s="4" t="s">
-        <v>1030</v>
+        <v>764</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
@@ -17778,16 +17793,16 @@
     </row>
     <row r="62" customHeight="1" spans="1:3">
       <c r="A62" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C62" s="2"/>
     </row>
     <row r="63" customHeight="1" spans="1:3">
       <c r="A63" s="6" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B63" s="7"/>
       <c r="C63" s="8">
